--- a/JsonConverter/ExcelFiles/CocktailBase.xlsx
+++ b/JsonConverter/ExcelFiles/CocktailBase.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18720" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22545" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <x:si>
     <x:t>아델하이드</x:t>
   </x:si>
@@ -67,13 +67,34 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_BronsonExt_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_PwdDelta_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Karmotrine_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Flanergide_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_Base_Mature_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Age_1</x:t>
   </x:si>
   <x:si>
     <x:t>숙성</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Base_Ice_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Ice_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Adelhyde_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1400,7 +1421,9 @@
       <x:c r="B4" s="3" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C4" s="13"/>
+      <x:c r="C4" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="D4" s="4"/>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1419,7 +1442,9 @@
       <x:c r="B5" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="5"/>
+      <x:c r="C5" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="D5" s="4"/>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
@@ -1438,7 +1463,9 @@
       <x:c r="B6" s="5" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" s="5"/>
+      <x:c r="C6" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="D6" s="4"/>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
@@ -1456,7 +1483,9 @@
       <x:c r="B7" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C7" s="3"/>
+      <x:c r="C7" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
@@ -1475,7 +1504,9 @@
       <x:c r="B8" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="3"/>
+      <x:c r="C8" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D8" s="4"/>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
@@ -1489,12 +1520,14 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="3"/>
+      <x:c r="C9" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="D9" s="4"/>
       <x:c r="E9" s="4"/>
       <x:c r="F9" s="4"/>
@@ -1508,12 +1541,14 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
-      <x:c r="C10" s="1"/>
+      <x:c r="C10" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="D10" s="4"/>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="4"/>
